--- a/assets/BOQ/SANO_ActualParserOutput_AAL5.xlsx
+++ b/assets/BOQ/SANO_ActualParserOutput_AAL5.xlsx
@@ -34,7 +34,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T05:32:24</t>
+    <t>2026-08-31T13:37:57</t>
   </si>
   <si>
     <t>Step</t>
